--- a/docs/data/predictions/2026-04-19_ST.xlsx
+++ b/docs/data/predictions/2026-04-19_ST.xlsx
@@ -541,12 +541,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -558,8 +562,10 @@
           <t>FOREMOST TEDDY</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -576,47 +582,79 @@
           <t>11/5/7/1/1/9</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="K2" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.9052</v>
-      </c>
-      <c r="R2" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6.4</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5.81</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5.9052</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -628,8 +666,10 @@
           <t>SUPER HONG KONG</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -646,47 +686,79 @@
           <t>10/1/2/6/1/8</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.815</v>
-      </c>
-      <c r="R3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>7</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5.815</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -698,8 +770,10 @@
           <t>HAILTOTHEVICTORS</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>10</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -716,47 +790,79 @@
           <t>1/8/4/7/7/2</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>10</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.6273</v>
-      </c>
-      <c r="R4" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8.4</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5.38</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5.6273</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -768,8 +874,10 @@
           <t>HAPPYDEARHAPPYDEER</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>9</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -786,47 +894,79 @@
           <t>11/9/7/13/2/2</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="K5" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>7.375</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.5366</v>
-      </c>
-      <c r="R5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9.199999999999999</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>7.375</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5.5366</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -838,8 +978,10 @@
           <t>GLORY CLOUD</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>9</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -856,47 +998,79 @@
           <t>9/9/6/10/1/2</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>10</v>
-      </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5.8198</v>
-      </c>
-      <c r="R6" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.8</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5.8198</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>2</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -908,8 +1082,10 @@
           <t>ISLAND BREEZES</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>10</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -926,47 +1102,79 @@
           <t>9/12/6/3/2/4</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>7.631578947368421</v>
-      </c>
-      <c r="P7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.6743</v>
-      </c>
-      <c r="R7" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>6.7</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6.14</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>7.631578947368421</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5.6743</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>3</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -978,8 +1186,10 @@
           <t>COLOURFUL WINNER</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>4</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -996,47 +1206,79 @@
           <t>2/4/10/7/11/2</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>9.052631578947368</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.4084</v>
-      </c>
-      <c r="R8" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8.800000000000001</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>9.052631578947368</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5.4084</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>4</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1048,8 +1290,10 @@
           <t>TRIUMPHANT WARRIOR</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>8</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1066,47 +1310,79 @@
           <t>6/4/5/5/7/3</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5.736842105263158</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.3744</v>
-      </c>
-      <c r="R9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>9</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5.43</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5.736842105263158</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5.3744</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1118,8 +1394,10 @@
           <t>RUN RUN SUNRISE</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>12</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1136,47 +1414,79 @@
           <t>2/1/2/10</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.7631</v>
-      </c>
-      <c r="R10" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>6.2</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5.7631</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>2</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1188,8 +1498,10 @@
           <t>TOURBILLON GOLFER</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>8</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1206,47 +1518,79 @@
           <t>3/6/9/3/11/2</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>10</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.6588</v>
-      </c>
-      <c r="R11" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6.9</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5.38</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5.6588</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
-        <v>3</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1258,8 +1602,10 @@
           <t>SYNERGY EXPRESS</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>2</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1276,47 +1622,79 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>6.210526315789473</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.3879</v>
-      </c>
-      <c r="R12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>9</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>6.210526315789473</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5.3879</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>4</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1328,8 +1706,10 @@
           <t>MAPOGO</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>3</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1346,47 +1726,79 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>6.210526315789473</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.3627</v>
-      </c>
-      <c r="R13" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>9.300000000000001</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6.210526315789473</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5.3627</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>4</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1398,8 +1810,10 @@
           <t>CHILL PARTNERS</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>12</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,47 +1830,79 @@
           <t>14/1/2/6/5</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>9.052631578947368</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5.6772</v>
-      </c>
-      <c r="R14" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5.3</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>9.052631578947368</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5.6772</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>2</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1468,8 +1914,10 @@
           <t>VOYAGE BOSS</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>10</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1486,47 +1934,79 @@
           <t>4/7/5/3/5/4</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5.736842105263158</v>
-      </c>
-      <c r="P15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.4213</v>
-      </c>
-      <c r="R15" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6.9</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5.736842105263158</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5.4213</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>3</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1538,8 +2018,10 @@
           <t>Z PRINCE</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>9</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1556,47 +2038,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>6.210526315789473</v>
-      </c>
-      <c r="P16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.2745</v>
-      </c>
-      <c r="R16" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="S16" t="n">
-        <v>7.9</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6.210526315789473</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5.2745</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>4</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1608,8 +2122,10 @@
           <t>BUCEPHALAS</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>14</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1626,47 +2142,79 @@
           <t>11/12/10/8/5/1</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>8.105263157894736</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.2378</v>
-      </c>
-      <c r="R17" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>8.300000000000001</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>8.105263157894736</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5.2378</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1678,8 +2226,10 @@
           <t>AMAZING DUCK</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>9</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1696,47 +2246,79 @@
           <t>5/2/6/2/3/13</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="K18" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.842105263157895</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.2683</v>
-      </c>
-      <c r="R18" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="S18" t="n">
-        <v>7.3</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3.842105263157895</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>5.2683</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="n">
-        <v>2</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1748,8 +2330,10 @@
           <t>FLYING BOOM</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>12</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1766,47 +2350,79 @@
           <t>3/1/6/4/9/5</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="K19" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>6.210526315789473</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.2038</v>
-      </c>
-      <c r="R19" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="S19" t="n">
-        <v>7.8</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>6.210526315789473</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5.2038</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
-        <v>3</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1818,8 +2434,10 @@
           <t>CLEANSWEEPER</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>13</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1836,47 +2454,79 @@
           <t>8</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>6.210526315789473</v>
-      </c>
-      <c r="P20" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.1989</v>
-      </c>
-      <c r="R20" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="S20" t="n">
-        <v>7.9</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>6.210526315789473</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5.1989</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>4</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1888,8 +2538,10 @@
           <t>PRESTIGE RICKY</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>2</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1906,47 +2558,79 @@
           <t>11/3/9/5/3/12</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="K21" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>6.210526315789473</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.1751</v>
-      </c>
-      <c r="R21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>8.1</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>6.210526315789473</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>5.1751</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>6</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1958,8 +2642,10 @@
           <t>SHOTGUN</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1976,47 +2662,79 @@
           <t>4/1/2/3/1/2</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>9</v>
-      </c>
-      <c r="K22" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4.705882352941177</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.4278</v>
-      </c>
-      <c r="R22" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.5</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>4.705882352941177</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6.4278</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>6</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>2</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2028,8 +2746,10 @@
           <t>SUPREME AGILITY</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>9</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2046,47 +2766,79 @@
           <t>2/9/1/3/4/2</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="K23" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>10</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.2594</v>
-      </c>
-      <c r="R23" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.1</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>6.2594</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="n">
-        <v>3</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2098,8 +2850,10 @@
           <t>CALIFORNIA STAR</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>14</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2116,47 +2870,79 @@
           <t>7/2/1/3/5/8</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>7.882352941176471</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.5022</v>
-      </c>
-      <c r="R24" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="S24" t="n">
-        <v>8.800000000000001</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>7.882352941176471</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5.5022</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>4</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2168,8 +2954,10 @@
           <t>SHANGHAI STYLE</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>2</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2186,47 +2974,79 @@
           <t>3/5/11/5/10/2</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="K25" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>5.764705882352941</v>
-      </c>
-      <c r="P25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.2895</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10.9</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>5.764705882352941</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>5.2895</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>7</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2238,8 +3058,10 @@
           <t>ARMOUR WAR EAGLE</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2256,47 +3078,79 @@
           <t>9/6/2/2/3/4</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>10</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.2664</v>
-      </c>
-      <c r="R26" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.5</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>6.2664</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>7</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>2</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2308,8 +3162,10 @@
           <t>JUICY DRAGON</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>8</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2326,47 +3182,79 @@
           <t>2/1/4/5/3/5</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="K27" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>4.9375</v>
-      </c>
-      <c r="P27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5.6236</v>
-      </c>
-      <c r="R27" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6.7</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6.52</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>4.9375</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>5.6236</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>7</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
-        <v>3</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2378,8 +3266,10 @@
           <t>ONE MAN SHOW</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>7</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2396,47 +3286,79 @@
           <t>5/5/3/2/5/11</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="K28" t="n">
-        <v>7</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="P28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5.4215</v>
-      </c>
-      <c r="R28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8.199999999999999</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>5.4215</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>7</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
-        <v>4</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2448,8 +3370,10 @@
           <t>LIGHT YEARS GLORY</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>6</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2466,47 +3390,79 @@
           <t>4/7/2/4/12/6</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="K29" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.2465</v>
-      </c>
-      <c r="R29" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="S29" t="n">
-        <v>9.800000000000001</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>5.2465</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2518,8 +3474,10 @@
           <t>AURORA PATCH</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>4</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2536,47 +3494,79 @@
           <t>2/7/1/5/1/2</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="K30" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>8.125</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6.3468</v>
-      </c>
-      <c r="R30" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.8</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>8.125</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>6.3468</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>8</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>2</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2588,8 +3578,10 @@
           <t>MR ENERGIA</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>10</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2606,47 +3598,79 @@
           <t>8/11/10/1/2/1</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="K31" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5.9156</v>
-      </c>
-      <c r="R31" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>5.9</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>7.24</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5.9156</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>8</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>3</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2658,8 +3682,10 @@
           <t>ROMANTIC SON</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>11</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2676,47 +3702,79 @@
           <t>3/4/1/1/7/5</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="K32" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>10</v>
-      </c>
-      <c r="P32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5.9024</v>
-      </c>
-      <c r="R32" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>6</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>5.9024</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>8</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>4</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2728,8 +3786,10 @@
           <t>BLAZING WIND</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>5</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2746,47 +3806,79 @@
           <t>4/3/7/1/3/4</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>7</v>
-      </c>
-      <c r="K33" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>5.125</v>
-      </c>
-      <c r="P33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5.8479</v>
-      </c>
-      <c r="R33" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="S33" t="n">
-        <v>6.3</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>5.125</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>5.8479</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>9</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2798,8 +3890,10 @@
           <t>SKY JEWELLERY</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>5</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2816,47 +3910,79 @@
           <t>1/2/1/4/1</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K34" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>10</v>
-      </c>
-      <c r="P34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6.6542</v>
-      </c>
-      <c r="R34" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.2</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>6.6542</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>9</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>2</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2868,8 +3994,10 @@
           <t>EVERYONE'S STAR</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>7</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2886,47 +4014,79 @@
           <t>7/5/5/2/3/2</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K35" t="n">
-        <v>7</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6.0956</v>
-      </c>
-      <c r="R35" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5.6</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>7.52</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>6.0956</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>9</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>3</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2938,8 +4098,10 @@
           <t>PERFECTDAY</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>2</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2956,47 +4118,79 @@
           <t>7/5/9/2/1/1</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="K36" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6.034</v>
-      </c>
-      <c r="R36" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5.9</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>7.86</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>6.034</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>9</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>4</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3008,8 +4202,10 @@
           <t>AEROVOLANIC</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>9</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3026,47 +4222,79 @@
           <t>1/1/2/8/3/4</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="K37" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>7</v>
-      </c>
-      <c r="P37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>5.8086</v>
-      </c>
-      <c r="R37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="S37" t="n">
-        <v>7.4</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>6.71</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>5.8086</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>10</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
-        <v>1</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3078,8 +4306,10 @@
           <t>SUPER EXPRESS</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>12</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3096,47 +4326,79 @@
           <t>2/2/2/1/2/2</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="K38" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="L38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>6.6213</v>
-      </c>
-      <c r="R38" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.7</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>9.19</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>6.6213</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
       </c>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>10</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
-        <v>2</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3148,8 +4410,10 @@
           <t>GOLD PATCH</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>6</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3166,47 +4430,79 @@
           <t>1/3/1</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="K39" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P39" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>6.335</v>
-      </c>
-      <c r="R39" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S39" t="n">
-        <v>4.9</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>6.335</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
       </c>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>10</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
-        <v>3</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3218,8 +4514,10 @@
           <t>ROBOT LUCKY STAR</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>7</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3236,47 +4534,79 @@
           <t>2/2/1/3</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K40" t="n">
-        <v>7</v>
-      </c>
-      <c r="L40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2</v>
-      </c>
-      <c r="P40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>6.097</v>
-      </c>
-      <c r="R40" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="S40" t="n">
-        <v>6.2</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6.097</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
       </c>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>10</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
-        <v>4</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3288,8 +4618,10 @@
           <t>SOUTH STAR</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>10</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3306,47 +4638,79 @@
           <t>4/10/7/1/2/7</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="K41" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5</v>
-      </c>
-      <c r="O41" t="n">
-        <v>10</v>
-      </c>
-      <c r="P41" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5.7197</v>
-      </c>
-      <c r="R41" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>9</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>5.7197</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>11</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>1</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3358,8 +4722,10 @@
           <t>WINNING WING</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>11</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3376,47 +4742,79 @@
           <t>3/1/5/2/1/1</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>9</v>
-      </c>
-      <c r="K42" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>8.559999999999999</v>
-      </c>
-      <c r="P42" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>6.5356</v>
-      </c>
-      <c r="R42" t="n">
-        <v>20</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4.2</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>8.559999999999999</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>6.5356</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
       </c>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>11</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>2</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3428,8 +4826,10 @@
           <t>PATCH OF COSMO</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>4</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3446,47 +4846,79 @@
           <t>4/3/9/1/1/6</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="K43" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="P43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>5.9291</v>
-      </c>
-      <c r="R43" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="S43" t="n">
-        <v>7.8</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>6.76</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5.9291</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
       </c>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>11</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
-        <v>3</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3498,8 +4930,10 @@
           <t>NEW FOREST</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>9</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3516,47 +4950,79 @@
           <t>9/11/8/1/1/4</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="K44" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N44" t="n">
-        <v>5</v>
-      </c>
-      <c r="O44" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P44" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>5.7382</v>
-      </c>
-      <c r="R44" t="n">
-        <v>9</v>
-      </c>
-      <c r="S44" t="n">
-        <v>9.4</v>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6.48</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5.7382</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
       </c>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>11</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="n">
-        <v>4</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3568,8 +5034,10 @@
           <t>GENTLEMEN LEGACY</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>5</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3586,39 +5054,67 @@
           <t>1/1/3/3/10/4</t>
         </is>
       </c>
-      <c r="J45" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="K45" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N45" t="n">
-        <v>5</v>
-      </c>
-      <c r="O45" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>5.6682</v>
-      </c>
-      <c r="R45" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10.1</v>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>5.6682</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
       </c>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3797,7 +5293,6 @@
           <t>2/7/1/5/1/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.050000000000001</v>
       </c>
@@ -3878,7 +5373,6 @@
           <t>8/11/10/1/2/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.24</v>
       </c>
@@ -3959,7 +5453,6 @@
           <t>3/4/1/1/7/5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.43</v>
       </c>
@@ -4040,7 +5533,6 @@
           <t>4/3/7/1/3/4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>7</v>
       </c>
@@ -4206,7 +5698,6 @@
           <t>6/4/3/11/3/7</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.86</v>
       </c>
@@ -4372,7 +5863,6 @@
           <t>7/9/8/6/9/9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.43</v>
       </c>
@@ -4453,7 +5943,6 @@
           <t>10/13/10/4/5/5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.05</v>
       </c>
@@ -4534,7 +6023,6 @@
           <t>1/4/4/6/10/7</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.76</v>
       </c>
@@ -4615,7 +6103,6 @@
           <t>10/8/2/8/12/7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>3</v>
       </c>
@@ -4827,7 +6314,6 @@
           <t>1/2/1/4/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -4908,7 +6394,6 @@
           <t>7/5/5/2/3/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.52</v>
       </c>
@@ -4989,7 +6474,6 @@
           <t>7/5/9/2/1/1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>7.86</v>
       </c>
@@ -5070,7 +6554,6 @@
           <t>1/1/2/8/3/4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.71</v>
       </c>
@@ -5151,7 +6634,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -5232,7 +6714,6 @@
           <t>5/5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -5313,7 +6794,6 @@
           <t>2/8/3/10/11/4</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.9</v>
       </c>
@@ -5394,7 +6874,6 @@
           <t>6/9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.67</v>
       </c>
@@ -5475,7 +6954,6 @@
           <t>5/8/10/6/6/6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.43</v>
       </c>
@@ -5556,7 +7034,6 @@
           <t>8/7/8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.33</v>
       </c>
@@ -5637,7 +7114,6 @@
           <t>14/11/7/9</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2</v>
       </c>
@@ -5718,7 +7194,6 @@
           <t>8/14</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.33</v>
       </c>
@@ -5930,7 +7405,6 @@
           <t>2/2/2/1/2/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>9.19</v>
       </c>
@@ -6011,7 +7485,6 @@
           <t>1/3/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>9.33</v>
       </c>
@@ -6092,7 +7565,6 @@
           <t>2/2/1/3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>8.9</v>
       </c>
@@ -6173,7 +7645,6 @@
           <t>4/10/7/1/2/7</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.71</v>
       </c>
@@ -6254,7 +7725,6 @@
           <t>2/5/2/9/2/8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.29</v>
       </c>
@@ -6335,7 +7805,6 @@
           <t>1/9/2/4/3/12</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.29</v>
       </c>
@@ -6416,7 +7885,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -6497,7 +7965,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5</v>
       </c>
@@ -6578,7 +8045,6 @@
           <t>10/12/10/6/6/1</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.86</v>
       </c>
@@ -6659,7 +8125,6 @@
           <t>3/4/11/3/8/10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.38</v>
       </c>
@@ -6740,7 +8205,6 @@
           <t>7/7/7/11/9/13</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.81</v>
       </c>
@@ -6821,7 +8285,6 @@
           <t>9/13/7</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.17</v>
       </c>
@@ -7033,7 +8496,6 @@
           <t>3/1/5/2/1/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>9</v>
       </c>
@@ -7114,7 +8576,6 @@
           <t>4/3/9/1/1/6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.76</v>
       </c>
@@ -7195,7 +8656,6 @@
           <t>9/11/8/1/1/4</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.48</v>
       </c>
@@ -7276,7 +8736,6 @@
           <t>1/1/3/3/10/4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.05</v>
       </c>
@@ -7442,7 +8901,6 @@
           <t>4/6/1/11/6/2</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.81</v>
       </c>
@@ -7523,7 +8981,6 @@
           <t>9/1/1/9/2/11</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5.29</v>
       </c>
@@ -7604,7 +9061,6 @@
           <t>2/13/1/9/8/3</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5.1</v>
       </c>
@@ -7685,7 +9141,6 @@
           <t>14/6/9/7/10/3</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.81</v>
       </c>
@@ -7766,7 +9221,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5</v>
       </c>
@@ -7847,7 +9301,6 @@
           <t>3/7/7/8/3/10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>3.67</v>
       </c>
@@ -7928,7 +9381,6 @@
           <t>5/12/2/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>3.8</v>
       </c>
@@ -8009,7 +9461,6 @@
           <t>9/9/7/4/9/8</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2.9</v>
       </c>
@@ -8090,7 +9541,6 @@
           <t>9/10/11/13/9/5</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2.43</v>
       </c>
@@ -8275,7 +9725,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>1</t>
@@ -8377,7 +9826,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>1</t>
@@ -8479,7 +9927,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
@@ -8581,7 +10028,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>2</t>
@@ -8683,7 +10129,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>9</t>
@@ -8785,7 +10230,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>8</t>
@@ -8887,7 +10331,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -8989,7 +10432,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>3</t>
@@ -9091,7 +10533,6 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>1</t>
@@ -9193,7 +10634,6 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>2</t>
@@ -9295,7 +10735,6 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>3</t>
@@ -9570,7 +11009,6 @@
           <t>11/5/7/1/1/9</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5.81</v>
       </c>
@@ -9651,7 +11089,6 @@
           <t>10/1/2/6/1/8</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6</v>
       </c>
@@ -9732,7 +11169,6 @@
           <t>1/8/4/7/7/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.38</v>
       </c>
@@ -9813,7 +11249,6 @@
           <t>11/9/7/13/2/2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.57</v>
       </c>
@@ -9894,7 +11329,6 @@
           <t>4/8/3/3/8/7</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.48</v>
       </c>
@@ -9975,7 +11409,6 @@
           <t>3/5/11/9/6/4</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.05</v>
       </c>
@@ -10056,7 +11489,6 @@
           <t>12/13/8/5/3/8</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.86</v>
       </c>
@@ -10137,7 +11569,6 @@
           <t>6/2/3/8/10/4</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.52</v>
       </c>
@@ -10218,7 +11649,6 @@
           <t>2/2/5/9/11/6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.76</v>
       </c>
@@ -10299,7 +11729,6 @@
           <t>5/12/10/7/12/5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.71</v>
       </c>
@@ -10380,7 +11809,6 @@
           <t>10/5/4/10/9/9</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.62</v>
       </c>
@@ -10461,7 +11889,6 @@
           <t>10/9/4/6/5/9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>3.62</v>
       </c>
@@ -10542,7 +11969,6 @@
           <t>5/9/10/7/9/6</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2.76</v>
       </c>
@@ -10839,7 +12265,6 @@
           <t>9/9/6/10/1/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6</v>
       </c>
@@ -10920,7 +12345,6 @@
           <t>9/12/6/3/2/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.14</v>
       </c>
@@ -11001,7 +12425,6 @@
           <t>2/4/10/7/11/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.52</v>
       </c>
@@ -11082,7 +12505,6 @@
           <t>6/4/5/5/7/3</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.43</v>
       </c>
@@ -11163,7 +12585,6 @@
           <t>6/3/2/6/3/6</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>6.05</v>
       </c>
@@ -11244,7 +12665,6 @@
           <t>3/12/13/1/10/5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.19</v>
       </c>
@@ -11325,7 +12745,6 @@
           <t>1/13/4/10/8/3</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.38</v>
       </c>
@@ -11406,7 +12825,6 @@
           <t>11/3/3/8/13/9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.14</v>
       </c>
@@ -11487,7 +12905,6 @@
           <t>5/9/10/10/9/3</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.52</v>
       </c>
@@ -11653,7 +13070,6 @@
           <t>7/6/9/12/9/2</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>4.05</v>
       </c>
@@ -11734,7 +13150,6 @@
           <t>7/9/10/10/11/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.19</v>
       </c>
@@ -11946,7 +13361,6 @@
           <t>2/1/2/10</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6</v>
       </c>
@@ -12027,7 +13441,6 @@
           <t>3/6/9/3/11/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.38</v>
       </c>
@@ -12108,7 +13521,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
@@ -12189,7 +13601,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5</v>
       </c>
@@ -12270,7 +13681,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -12351,7 +13761,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -12432,7 +13841,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -12513,7 +13921,6 @@
           <t>6/2/13/14/10/5</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.05</v>
       </c>
@@ -12594,7 +14001,6 @@
           <t>1/4/7/6/7/7</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.81</v>
       </c>
@@ -12760,7 +14166,6 @@
           <t>11/8/7/11/13/8</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.67</v>
       </c>
@@ -12841,7 +14246,6 @@
           <t>4/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.67</v>
       </c>
@@ -12922,7 +14326,6 @@
           <t>5/3/10/11/6/9</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2.86</v>
       </c>
@@ -13003,7 +14406,6 @@
           <t>12/13</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1</v>
       </c>
@@ -13215,7 +14617,6 @@
           <t>14/1/2/6/5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5.93</v>
       </c>
@@ -13296,7 +14697,6 @@
           <t>4/7/5/3/5/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.71</v>
       </c>
@@ -13377,7 +14777,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
@@ -13458,7 +14857,6 @@
           <t>11/12/10/8/5/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.71</v>
       </c>
@@ -13539,7 +14937,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -13620,7 +15017,6 @@
           <t>7/10/5/7/8/8</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2.57</v>
       </c>
@@ -13701,7 +15097,6 @@
           <t>2/4/5/12/8/12</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2.67</v>
       </c>
@@ -13867,7 +15262,6 @@
           <t>1/8/10/5/7/12</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.76</v>
       </c>
@@ -13948,7 +15342,6 @@
           <t>6/4/9/6/11/7</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.9</v>
       </c>
@@ -14029,7 +15422,6 @@
           <t>10/10/13/11/11/10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1</v>
       </c>
@@ -14110,7 +15502,6 @@
           <t>9/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.33</v>
       </c>
@@ -14191,7 +15582,6 @@
           <t>8/10/11/12/13/12</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
@@ -14272,7 +15662,6 @@
           <t>11/13/10/10/12</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1</v>
       </c>
@@ -14484,7 +15873,6 @@
           <t>5/2/6/2/3/13</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5.57</v>
       </c>
@@ -14565,7 +15953,6 @@
           <t>3/1/6/4/9/5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>4.95</v>
       </c>
@@ -14646,7 +16033,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
@@ -14727,7 +16113,6 @@
           <t>11/3/9/5/3/12</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.24</v>
       </c>
@@ -14808,7 +16193,6 @@
           <t>1/3/6/8/7</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.07</v>
       </c>
@@ -14889,7 +16273,6 @@
           <t>4/7/2/3/8/9</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.43</v>
       </c>
@@ -15055,7 +16438,6 @@
           <t>12/14/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1</v>
       </c>
@@ -15136,7 +16518,6 @@
           <t>8/7/12/12/14</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1.33</v>
       </c>
@@ -15217,7 +16598,6 @@
           <t>10/4/11/12/12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.67</v>
       </c>
@@ -15298,7 +16678,6 @@
           <t>9/12/6/9/8/7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.48</v>
       </c>
@@ -15379,7 +16758,6 @@
           <t>13/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1</v>
       </c>
@@ -15460,7 +16838,6 @@
           <t>5/12/10/10/8</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1.6</v>
       </c>
@@ -15541,7 +16918,6 @@
           <t>11/10/11/12/12/13</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1</v>
       </c>
@@ -15753,7 +17129,6 @@
           <t>4/1/2/3/1/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>9</v>
       </c>
@@ -15834,7 +17209,6 @@
           <t>2/9/1/3/4/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.57</v>
       </c>
@@ -15915,7 +17289,6 @@
           <t>7/2/1/3/5/8</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.71</v>
       </c>
@@ -15996,7 +17369,6 @@
           <t>3/5/11/5/10/2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.76</v>
       </c>
@@ -16077,7 +17449,6 @@
           <t>13/7/11/7/2/10</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>3.48</v>
       </c>
@@ -16158,7 +17529,6 @@
           <t>6/3/6/9/2/6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.19</v>
       </c>
@@ -16239,7 +17609,6 @@
           <t>1/11/7/4/7/7</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.71</v>
       </c>
@@ -16320,7 +17689,6 @@
           <t>7/7/13/9/2/12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.38</v>
       </c>
@@ -16401,7 +17769,6 @@
           <t>4/4/4/9/8/7</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.43</v>
       </c>
@@ -16482,7 +17849,6 @@
           <t>10/13/11/11/9/12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.24</v>
       </c>
@@ -16563,7 +17929,6 @@
           <t>9/10/7/13</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.7</v>
       </c>
@@ -16644,7 +18009,6 @@
           <t>9/10/11/10/10/9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.33</v>
       </c>
@@ -16725,7 +18089,6 @@
           <t>9/13/11</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1.17</v>
       </c>
@@ -16806,7 +18169,6 @@
           <t>7/10/14/9/9</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1.73</v>
       </c>
@@ -17018,7 +18380,6 @@
           <t>9/6/2/2/3/4</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.1</v>
       </c>
@@ -17099,7 +18460,6 @@
           <t>2/1/4/5/3/5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.52</v>
       </c>
@@ -17180,7 +18540,6 @@
           <t>5/5/3/2/5/11</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.05</v>
       </c>
@@ -17261,7 +18620,6 @@
           <t>4/7/2/4/12/6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.38</v>
       </c>
@@ -17342,7 +18700,6 @@
           <t>9/4/4/6/6/8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>3.81</v>
       </c>
@@ -17423,7 +18780,6 @@
           <t>5/8/6/6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.7</v>
       </c>
@@ -17504,7 +18860,6 @@
           <t>3/3/3/5/9/8</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.29</v>
       </c>
@@ -17585,7 +18940,6 @@
           <t>12/2/7/7/11/8</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.71</v>
       </c>
@@ -17666,7 +19020,6 @@
           <t>13/13/10/7/6/14</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.1</v>
       </c>
@@ -17747,7 +19100,6 @@
           <t>9/11/11</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.17</v>
       </c>
@@ -17828,7 +19180,6 @@
           <t>2/2/5/9/12/12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.9</v>
       </c>
@@ -17909,7 +19260,6 @@
           <t>12/13/10/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1</v>
       </c>
